--- a/liga_eliminacao/datasets_liga_eliminacao/links_times_cartola_liga_eliminacao_20.xlsx
+++ b/liga_eliminacao/datasets_liga_eliminacao/links_times_cartola_liga_eliminacao_20.xlsx
@@ -67,7 +67,7 @@
     <t>GrioTeam</t>
   </si>
   <si>
-    <t>GE Bebum</t>
+    <t>GE Xavanchesteer</t>
   </si>
   <si>
     <t xml:space="preserve">bugredasmissões </t>
